--- a/data/metadata/Cases_excluded.xlsx
+++ b/data/metadata/Cases_excluded.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hanleyb/Documents/GitHub/VAULT_Breast/data/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91A877C-7DB0-1C4B-8EAD-9C59B1B90F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D00468E-DFF1-5042-904D-E42E4D1349E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25600" yWindow="-7340" windowWidth="25600" windowHeight="28300" xr2:uid="{467A4392-D00F-6048-87CA-441FFB439418}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17740" xr2:uid="{467A4392-D00F-6048-87CA-441FFB439418}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="50">
   <si>
     <t>HF008</t>
   </si>
@@ -180,6 +180,15 @@
   </si>
   <si>
     <t>Phyllodes tumour</t>
+  </si>
+  <si>
+    <t>HF079</t>
+  </si>
+  <si>
+    <t>160 days in formalin</t>
+  </si>
+  <si>
+    <t>23</t>
   </si>
 </sst>
 </file>
@@ -222,20 +231,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -589,12 +590,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C09FC151-01C1-9742-BA35-5D81D025A310}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.1640625" bestFit="1" customWidth="1"/>
@@ -604,235 +605,235 @@
       <c r="A1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="2">
         <v>38</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>38</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="2">
         <v>7</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>7</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="2">
         <v>33</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>55</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="2">
         <v>32</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>32</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="5">
-        <v>24</v>
-      </c>
-      <c r="E6" s="2">
-        <v>24</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="D6" s="2">
+        <v>24</v>
+      </c>
+      <c r="E6" s="1">
+        <v>24</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="2">
         <v>18</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>45</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="2">
         <v>27</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>27</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="2">
         <v>13</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>35</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="2">
         <v>45</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="1">
         <v>45</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="1" t="s">
         <v>38</v>
       </c>
       <c r="H10" t="s">
@@ -840,51 +841,51 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="2">
         <v>7</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="1">
         <v>50</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="1" t="s">
         <v>18</v>
       </c>
       <c r="H12" t="s">
@@ -892,25 +893,25 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E13" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="1" t="s">
         <v>41</v>
       </c>
       <c r="H13" t="s">
@@ -918,72 +919,95 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="2">
         <v>18</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="1">
         <v>18</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="1">
         <v>38</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="2">
         <v>17</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="1">
         <v>25</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="1" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="1">
+        <v>23</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1002,7 +1026,7 @@
       <formula>$T19="2= Renal"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D9:F10 E11:F11 D12:F12 F13 D14:F16">
+  <conditionalFormatting sqref="D9:F10 E11:F11 D12:F12 F13 D14:F16 E17:F17">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>$T22="2= Renal"</formula>
     </cfRule>
